--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484526_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484526_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4091</v>
+        <v>4.7308</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4957</v>
+        <v>4.7431</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0122</v>
       </c>
       <c r="G2" t="n">
         <v>3.0775</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.4712</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4419</v>
+        <v>-0.1945</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3509</v>
+        <v>-0.2766</v>
       </c>
       <c r="V2" t="n">
         <v>3.0407</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9782</v>
+        <v>3.2138</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5971</v>
+        <v>2.2291</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3811</v>
+        <v>0.9847</v>
       </c>
       <c r="G3" t="n">
         <v>2.5244</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2809</v>
+        <v>-0.0453</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.2677</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6188</v>
+        <v>0.2224</v>
       </c>
       <c r="V3" t="n">
         <v>0.1848</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0408</v>
+        <v>0.7553</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0858</v>
+        <v>-0.2988</v>
       </c>
       <c r="F4" t="n">
-        <v>0.955</v>
+        <v>1.0541</v>
       </c>
       <c r="G4" t="n">
         <v>2.1294</v>
@@ -766,13 +766,13 @@
         <v>0.3665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3775</v>
+        <v>0.092</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8054</v>
+        <v>0.4208</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4279</v>
+        <v>-0.3288</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AVIÑO GOMEZ-SENENT</t>
+          <t>J. AVINO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.4979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>1.3029</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>0.3655</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-1.9488</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.3144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>0.6758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>-0.7093</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.3851</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.3103</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.2395</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.9293</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.6452</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.6388</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AVINO GOMEZ-SENENT</t>
+          <t>J. AVIÑO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2095</v>
+        <v>0.3251</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0144</v>
+        <v>0.3251</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3655</v>
+        <v>0.3251</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9488</v>
+        <v>0.3251</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3144</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6758</v>
+        <v>0.3251</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7093</v>
+        <v>0.3251</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3851</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3103</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2395</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9293</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9336</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2949</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6388</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5359</v>
+        <v>-0.4532</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7496</v>
+        <v>1.7085</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2855</v>
+        <v>-2.1616</v>
       </c>
       <c r="G8" t="n">
         <v>1.0473</v>
@@ -1078,13 +1078,13 @@
         <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7968</v>
+        <v>-0.714</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4374</v>
+        <v>0.3963</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2342</v>
+        <v>-1.1103</v>
       </c>
       <c r="V8" t="n">
         <v>0.4964</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.901</v>
+        <v>-2.239</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5511</v>
+        <v>-3.8395</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6501</v>
+        <v>1.6006</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7163</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>0.792</v>
+        <v>0.454</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5664</v>
+        <v>0.2779</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2256</v>
+        <v>0.1761</v>
       </c>
       <c r="V9" t="n">
         <v>1.5889</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.684</v>
+        <v>-2.802</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8177</v>
+        <v>-4.01</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1337</v>
+        <v>1.208</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6808</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5624</v>
+        <v>0.4444</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4917</v>
+        <v>0.2994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0706</v>
+        <v>0.145</v>
       </c>
       <c r="V10" t="n">
         <v>1.267</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6987</v>
+        <v>-2.8381</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5458</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1528</v>
+        <v>-3.7014</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9137</v>
+        <v>-0.2069</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1282</v>
+        <v>0.54</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0419</v>
+        <v>-0.747</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8293</v>
+        <v>1.0237</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8854</v>
+        <v>1.5139</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7147</v>
+        <v>-0.4902</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0843</v>
+        <v>-1.2306</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7572</v>
+        <v>-0.9739</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.2567</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3704</v>
+        <v>-0.1092</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8778</v>
+        <v>0.434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5074</v>
+        <v>-0.5432</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3387</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3054</v>
+        <v>-3.0778</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5199</v>
+        <v>-0.8754</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8253</v>
+        <v>-2.2024</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2069</v>
+        <v>-0.9137</v>
       </c>
       <c r="H12" t="n">
-        <v>0.54</v>
+        <v>0.1282</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.747</v>
+        <v>-1.0419</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0237</v>
+        <v>-0.8293</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5139</v>
+        <v>0.8854</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4902</v>
+        <v>-1.7147</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2306</v>
+        <v>-0.0843</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9739</v>
+        <v>-0.7572</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2567</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5766</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0905</v>
+        <v>0.5483</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6671</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3387</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.512100000000002</v>
+        <v>-1.236999999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>2.523200000000001</v>
+        <v>2.7986</v>
       </c>
       <c r="F13" t="n">
         <v>-4.0351</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6017</v>
+        <v>4.601700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6871</v>
+        <v>-0.6871000000000002</v>
       </c>
       <c r="I13" t="n">
         <v>5.288800000000001</v>
@@ -1444,7 +1444,7 @@
         <v>7.8108</v>
       </c>
       <c r="K13" t="n">
-        <v>7.968299999999999</v>
+        <v>7.9683</v>
       </c>
       <c r="L13" t="n">
         <v>-0.1574999999999998</v>
@@ -1468,13 +1468,13 @@
         <v>10.9954</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2784</v>
+        <v>-1.0032</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6327</v>
+        <v>1.9081</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9113</v>
+        <v>-2.9112</v>
       </c>
       <c r="V13" t="n">
         <v>1.578500000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4102</v>
+        <v>3.6644</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1051</v>
+        <v>3.855</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6948</v>
+        <v>-0.1907</v>
       </c>
       <c r="G14" t="n">
         <v>2.311</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>1.684</v>
+        <v>0.9382</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7014</v>
+        <v>0.4514</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0174</v>
+        <v>0.4868</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3178</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3152</v>
+        <v>3.4433</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2096</v>
+        <v>3.498</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1056</v>
+        <v>-0.0548</v>
       </c>
       <c r="G15" t="n">
         <v>2.0601</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8478</v>
+        <v>0.9759</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3643</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4835</v>
+        <v>0.3231</v>
       </c>
       <c r="V15" t="n">
         <v>1.1403</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9745</v>
+        <v>3.0353</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5982</v>
+        <v>2.491</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6237</v>
+        <v>0.5444</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7626</v>
+        <v>2.6636</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8651</v>
+        <v>1.2982</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8974</v>
+        <v>1.3654</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5487</v>
+        <v>2.925</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0683</v>
+        <v>2.2325</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4804</v>
+        <v>0.6925</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2139</v>
+        <v>-0.2614</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7968</v>
+        <v>-0.9342</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.417</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
         <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0629</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6026</v>
+        <v>-0.1904</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6655</v>
+        <v>0.1898</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7842</v>
+        <v>0.189</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5444</v>
+        <v>1.5889</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7602</v>
+        <v>-1.3999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7255</v>
+        <v>3.0352</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4333</v>
+        <v>2.7906</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2923</v>
+        <v>0.2446</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6636</v>
+        <v>-1.7626</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2982</v>
+        <v>-0.8651</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3654</v>
+        <v>-0.8974</v>
       </c>
       <c r="J17" t="n">
-        <v>2.925</v>
+        <v>-0.5487</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2325</v>
+        <v>-0.0683</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6925</v>
+        <v>-0.4804</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2614</v>
+        <v>-1.2139</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9342</v>
+        <v>-0.7968</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.417</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1833</v>
+        <v>2.0158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3103</v>
+        <v>0.9977</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2481</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0622</v>
+        <v>0.2029</v>
       </c>
       <c r="V17" t="n">
-        <v>0.189</v>
+        <v>1.7842</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5889</v>
+        <v>2.5444</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MATEO LAZARO</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0828</v>
+        <v>0.9971</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0112</v>
+        <v>0.6821</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9284</v>
+        <v>0.315</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5213</v>
+        <v>0.4219</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2098</v>
+        <v>-0.2223</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.731</v>
+        <v>0.6442</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5904</v>
+        <v>0.7518</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7057</v>
+        <v>0.0433</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1154</v>
+        <v>0.7085</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1116</v>
+        <v>-0.3299</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4959</v>
+        <v>-0.2656</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3843</v>
+        <v>-0.0643</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9977</v>
+        <v>-0.0234</v>
       </c>
       <c r="T20" t="n">
-        <v>1.353</v>
+        <v>-0.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6448</v>
+        <v>0.0464</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7602</v>
+        <v>-0.3178</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6606</v>
+        <v>-0.3178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0496</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9705</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4219</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2223</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6442</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7518</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0433</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7085</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2656</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0643</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2187</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1896</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3178</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. MATEO LAZARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.4912</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.5305</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-1.0393</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.5213</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.2098</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.731</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.5904</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.7057</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.1154</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-1.1116</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.3843</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.4061</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.8722</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.5339</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.6606</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9192</v>
+        <v>-1.6243</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1836</v>
+        <v>-2.1452</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2645</v>
+        <v>0.5209</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3267</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0068</v>
+        <v>0.3017</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2255</v>
+        <v>0.264</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2187</v>
+        <v>0.0377</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9658</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3274</v>
+        <v>-2.5237</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5708</v>
+        <v>-4.7054</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2434</v>
+        <v>2.1817</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7123</v>
@@ -2326,13 +2326,13 @@
         <v>2.5656</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9466</v>
+        <v>-0.1429</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.138</v>
+        <v>-0.2726</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8086</v>
+        <v>0.1297</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3178</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.092</v>
+        <v>-4.2776</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4651</v>
+        <v>-3.0805</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6269</v>
+        <v>-1.1971</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8864</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.545</v>
+        <v>0.2694</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1086</v>
+        <v>0.4932</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6536</v>
+        <v>-0.2238</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3937</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5584</v>
+        <v>-4.7338</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9243</v>
+        <v>-4.732</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6341</v>
+        <v>-0.0017</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7005</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4223</v>
+        <v>0.4023</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2767</v>
+        <v>-0.0844</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1456</v>
+        <v>0.4868</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6189</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.511899999999999</v>
+        <v>5.358200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>4.035200000000001</v>
+        <v>4.035199999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.5231</v>
+        <v>1.323</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.602099999999998</v>
+        <v>-4.6021</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6869000000000001</v>
+        <v>0.686900000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-5.2888</v>
@@ -2560,13 +2560,13 @@
         <v>17.4093</v>
       </c>
       <c r="S27" t="n">
-        <v>1.278300000000001</v>
+        <v>5.124400000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>2.911300000000001</v>
+        <v>2.9113</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.6329</v>
+        <v>2.2133</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5785</v>
